--- a/要件定義兼設計書.xlsx
+++ b/要件定義兼設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pleiades\2026-06\workspace\springportfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5519609-E5FF-436F-BEDD-A32FF86E2F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0876BD30-EC07-4C8E-A9BF-5C4E83460EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="757" xr2:uid="{C9271884-C87F-40D4-9F78-D9852228CE21}"/>
   </bookViews>
@@ -23,6 +23,8 @@
     <sheet name="月別支出" sheetId="11" r:id="rId8"/>
     <sheet name="年間支出" sheetId="12" r:id="rId9"/>
     <sheet name="支出比較" sheetId="13" r:id="rId10"/>
+    <sheet name="ユーザー設定" sheetId="14" r:id="rId11"/>
+    <sheet name="支出登録" sheetId="15" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="119">
   <si>
     <t>番号</t>
     <rPh sb="0" eb="2">
@@ -823,6 +825,560 @@
     </rPh>
     <rPh sb="14" eb="16">
       <t>ヒカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示部品</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ブヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ログイン実行ボタン</t>
+    <rPh sb="5" eb="7">
+      <t>ジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ユーザー登録ボタン</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ログインせずにURLを実行した場合、初回遷移する</t>
+    <rPh sb="12" eb="14">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ショカイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ID入力フォーム</t>
+    <rPh sb="3" eb="5">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・パスワード入力フォーム</t>
+    <rPh sb="6" eb="8">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ID、パスワードの入力を読み取り、DBのusersに登録があるかを確認して、ログイン処理を行う</t>
+    <rPh sb="10" eb="12">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ログインに成功した場合は、当月支出画面に遷移する</t>
+    <rPh sb="6" eb="8">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="14" eb="20">
+      <t>トウゲツシシュツガメン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ログインに失敗した場合は、メッセージを表示したログイン画面に遷移する</t>
+    <rPh sb="6" eb="8">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ユーザー登録ボタンを押した場合は、ユーザー登録画面に遷移する</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="22" eb="26">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示部品</t>
+    <rPh sb="0" eb="4">
+      <t>ヒョウジブヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ID入力フォーム(必須)</t>
+    <rPh sb="3" eb="5">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・パスワード入力フォーム(必須)</t>
+    <rPh sb="6" eb="8">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・パスワード再入力フォーム(必須)</t>
+    <rPh sb="6" eb="7">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・登録実行ボタン</t>
+    <rPh sb="1" eb="5">
+      <t>トウロクジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・メッセージ表示部品</t>
+    <rPh sb="6" eb="8">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ブヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・登録の際にID、パスワードのチェックを行う</t>
+    <rPh sb="1" eb="3">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・収入入力フォーム</t>
+    <rPh sb="1" eb="3">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・氏名入力フォーム(必須)</t>
+    <rPh sb="1" eb="3">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・登録が完了した場合はログイン画面に遷移する</t>
+    <rPh sb="1" eb="3">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・登録が失敗した場合はメッセージを表示し同じ画面に遷移する</t>
+    <rPh sb="1" eb="3">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当月支出</t>
+    <rPh sb="0" eb="4">
+      <t>トウゲツシシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・氏名表示部品</t>
+    <rPh sb="1" eb="3">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ブヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・当月表示部品</t>
+    <rPh sb="1" eb="3">
+      <t>トウゲツ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>ヒョウジブヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・当月支出データ表示リスト</t>
+    <rPh sb="1" eb="5">
+      <t>トウゲツシシュツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・月別支出遷移ボタン</t>
+    <rPh sb="1" eb="5">
+      <t>ツキベツシシュツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・年間支出遷移ボタン</t>
+    <rPh sb="1" eb="5">
+      <t>ネンカンシシュツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・支出比較遷移ボタン</t>
+    <rPh sb="1" eb="5">
+      <t>シシュツヒカク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ユーザー設定遷移ボタン</t>
+    <rPh sb="5" eb="7">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・支出登録遷移ボタン</t>
+    <rPh sb="1" eb="5">
+      <t>シシュツトウロク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ログイン画面から受けたデータを元にユーザーが登録した氏名を表示する</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・PCの日付から本日の日付を表示する</t>
+    <rPh sb="4" eb="6">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ホンジツ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・当月の支出をDBから取得し、日付、大項目、項目、名称、金額の項目をリストにして表示する</t>
+    <rPh sb="1" eb="3">
+      <t>トウゲツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>ダイコウモク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>メイショウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・登録実行ボタンを押すとID、パスワード、氏名、収入の入力を読み取り問題ない場合DBのusersに登録する</t>
+    <rPh sb="1" eb="5">
+      <t>トウロクジッコウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・当月の支出データが存在しない場合はメッセージを表示する</t>
+    <rPh sb="1" eb="3">
+      <t>トウゲツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>月別支出</t>
+    <rPh sb="0" eb="4">
+      <t>ツキベツシシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>年間支出</t>
+    <rPh sb="0" eb="4">
+      <t>ネンカンシシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支出比較</t>
+    <rPh sb="0" eb="4">
+      <t>シシュツヒカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー設定</t>
+    <rPh sb="4" eb="6">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・月別支出データリスト</t>
+    <rPh sb="1" eb="3">
+      <t>ツキベツ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・当月支出遷移ボタン</t>
+    <rPh sb="1" eb="5">
+      <t>トウゲツシシュツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・メッセージ表示部品</t>
+    <rPh sb="6" eb="10">
+      <t>ヒョウジブヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・年間支出データリスト</t>
+    <rPh sb="1" eb="5">
+      <t>ネンカンシシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支出登録</t>
+    <rPh sb="0" eb="4">
+      <t>シシュツトウロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3263,15 +3819,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>655320</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3285,12 +3841,14 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7520940" y="822960"/>
-          <a:ext cx="2667000" cy="243840"/>
+        <a:xfrm flipV="1">
+          <a:off x="7528560" y="1066800"/>
+          <a:ext cx="2659380" cy="906780"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 21920"/>
+          </a:avLst>
         </a:prstGeom>
         <a:ln>
           <a:solidFill>
@@ -3318,15 +3876,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>655320</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3340,12 +3898,14 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7520940" y="1043940"/>
-          <a:ext cx="2667000" cy="243840"/>
+        <a:xfrm flipV="1">
+          <a:off x="7528560" y="1287780"/>
+          <a:ext cx="2659380" cy="937260"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 38252"/>
+          </a:avLst>
         </a:prstGeom>
         <a:ln>
           <a:solidFill>
@@ -3372,16 +3932,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>662940</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3395,9 +3955,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7513320" y="1295400"/>
-          <a:ext cx="2667000" cy="243840"/>
+        <a:xfrm flipV="1">
+          <a:off x="7520940" y="1546860"/>
+          <a:ext cx="2659380" cy="899160"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -3429,142 +3989,30 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>883920</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="7" name="コネクタ: カギ線 6">
+        <xdr:cNvPr id="14" name="直線コネクタ 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19EB8126-4CF1-5CD6-E3E3-562D36509E83}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4551F13-0989-EEF0-6981-EE3D62C33896}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="3154680" y="121920"/>
-          <a:ext cx="6012180" cy="739140"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 27567"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>297180</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="10" name="直線コネクタ 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3EF6B60-6D6A-5250-590E-35527C157AF7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="9159240" y="137160"/>
-          <a:ext cx="7620" cy="701040"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>662940</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="12" name="直線コネクタ 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71ED9B07-D930-44CF-800E-4A92B9342D52}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="9166860" y="830580"/>
-          <a:ext cx="1028700" cy="0"/>
+        <a:xfrm>
+          <a:off x="3154680" y="807720"/>
+          <a:ext cx="7048500" cy="7620"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -4048,7 +4496,45 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C6B2588-BA90-4F8D-983C-CC159D52FDE0}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="36.6" x14ac:dyDescent="0.45">
+      <c r="A1" s="10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8D3CDDB-8559-466E-84AE-46905D21429B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="36.6" x14ac:dyDescent="0.45">
+      <c r="A1" s="10" t="s">
+        <v>113</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD431F7A-5A72-48E5-8D03-640DACD1A7B8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="36.6" x14ac:dyDescent="0.45">
+      <c r="A1" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4222,7 +4708,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537B1608-6FB7-403A-B22E-1A6A708FF8DA}">
-  <dimension ref="B1:Q13"/>
+  <dimension ref="B1:Q14"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="13.19921875" bestFit="1" customWidth="1"/>
@@ -4239,11 +4725,6 @@
       </c>
       <c r="C2" s="25"/>
       <c r="D2" s="26"/>
-      <c r="H2" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="I2" s="25"/>
-      <c r="J2" s="26"/>
       <c r="O2" s="24" t="s">
         <v>53</v>
       </c>
@@ -4260,15 +4741,6 @@
       <c r="D3" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="H3" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="I3" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="J3" s="23" t="s">
-        <v>66</v>
-      </c>
       <c r="O3" s="21" t="s">
         <v>67</v>
       </c>
@@ -4289,15 +4761,6 @@
       <c r="D4" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="H4" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J4" s="18" t="s">
-        <v>70</v>
-      </c>
       <c r="O4" s="13" t="s">
         <v>44</v>
       </c>
@@ -4316,13 +4779,6 @@
       <c r="D5" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="H5" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="18" t="s">
-        <v>70</v>
-      </c>
       <c r="O5" s="13" t="s">
         <v>60</v>
       </c>
@@ -4333,7 +4789,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B6" s="13" t="s">
         <v>47</v>
       </c>
@@ -4341,13 +4797,6 @@
       <c r="D6" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="H6" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="18" t="s">
-        <v>70</v>
-      </c>
       <c r="O6" s="13" t="s">
         <v>54</v>
       </c>
@@ -4356,7 +4805,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B7" s="13" t="s">
         <v>46</v>
       </c>
@@ -4364,13 +4813,11 @@
       <c r="D7" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="H7" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="18" t="s">
-        <v>70</v>
-      </c>
+      <c r="H7" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" s="25"/>
+      <c r="J7" s="26"/>
       <c r="O7" s="13" t="s">
         <v>55</v>
       </c>
@@ -4387,12 +4834,14 @@
       <c r="D8" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="18" t="s">
-        <v>73</v>
+      <c r="H8" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>66</v>
       </c>
       <c r="O8" s="13" t="s">
         <v>58</v>
@@ -4402,7 +4851,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B9" s="13" t="s">
         <v>49</v>
       </c>
@@ -4410,12 +4859,14 @@
       <c r="D9" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="H9" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="I9" s="19"/>
-      <c r="J9" s="20" t="s">
-        <v>68</v>
+      <c r="H9" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>70</v>
       </c>
       <c r="O9" s="13" t="s">
         <v>56</v>
@@ -4433,6 +4884,13 @@
       <c r="D10" s="18" t="s">
         <v>71</v>
       </c>
+      <c r="H10" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="18" t="s">
+        <v>70</v>
+      </c>
       <c r="O10" s="13" t="s">
         <v>57</v>
       </c>
@@ -4449,6 +4907,13 @@
       <c r="D11" s="18" t="s">
         <v>71</v>
       </c>
+      <c r="H11" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="18" t="s">
+        <v>70</v>
+      </c>
       <c r="O11" s="13" t="s">
         <v>63</v>
       </c>
@@ -4465,6 +4930,13 @@
       <c r="D12" s="18" t="s">
         <v>71</v>
       </c>
+      <c r="H12" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="18" t="s">
+        <v>70</v>
+      </c>
       <c r="O12" s="15" t="s">
         <v>59</v>
       </c>
@@ -4481,11 +4953,27 @@
       <c r="D13" s="20" t="s">
         <v>69</v>
       </c>
+      <c r="H13" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="H14" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="I14" s="19"/>
+      <c r="J14" s="20" t="s">
+        <v>68</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="H7:J7"/>
     <mergeCell ref="O2:Q2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
@@ -4496,9 +4984,75 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DEECB3F-B623-4586-A047-3F1FB05265A1}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="36.6" x14ac:dyDescent="0.45">
+      <c r="A1" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4506,9 +5060,80 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B694F0B-D30C-4B05-B840-D26C979D5CEF}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="36.6" x14ac:dyDescent="0.45">
+      <c r="A1" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4516,9 +5141,90 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC03E0FC-FD83-4EFF-8917-69D267C31BBB}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="36.6" x14ac:dyDescent="0.45">
+      <c r="A1" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4526,9 +5232,50 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFE29E1A-E720-45DE-8213-46E01EB83BED}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="36.6" x14ac:dyDescent="0.45">
+      <c r="A1" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4536,9 +5283,45 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF3CB4E6-DBF0-4C32-B8DB-B2B07996689E}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="36.6" x14ac:dyDescent="0.45">
+      <c r="A1" s="10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/要件定義兼設計書.xlsx
+++ b/要件定義兼設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pleiades\2026-06\workspace\springportfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0876BD30-EC07-4C8E-A9BF-5C4E83460EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145285B5-A101-409C-8804-8B865025BB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="757" xr2:uid="{C9271884-C87F-40D4-9F78-D9852228CE21}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="164">
   <si>
     <t>番号</t>
     <rPh sb="0" eb="2">
@@ -731,10 +731,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>paymentd_data</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>type1</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1379,6 +1375,622 @@
     <t>支出登録</t>
     <rPh sb="0" eb="4">
       <t>シシュツトウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・本年表示部品</t>
+    <rPh sb="1" eb="3">
+      <t>ホンネン</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>ヒョウジブヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・PCの日付から本年の年を表示する</t>
+    <rPh sb="4" eb="6">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ホンネン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・本年の1月から12月までの支出データを月別に大項目ごとにまとめてリスト表示する</t>
+    <rPh sb="1" eb="3">
+      <t>ホンネン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ツキベツ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>ダイコウモク</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・本年のデータが存在しない場合はメッセージを表示する</t>
+    <rPh sb="1" eb="3">
+      <t>ホンネン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・本年表示部品</t>
+    <rPh sb="1" eb="7">
+      <t>ホンネンヒョウジブヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・本年の支出データを大項目ごとにまとめてリスト表示する</t>
+    <rPh sb="1" eb="3">
+      <t>ホンネン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ダイコウモク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・本年のデータがない場合はメッセージを表示する</t>
+    <rPh sb="1" eb="3">
+      <t>ホンネン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・収入表示部品</t>
+    <rPh sb="1" eb="3">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>ヒョウジブヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・投資項目表示部品</t>
+    <rPh sb="1" eb="9">
+      <t>トウシコウモクヒョウジブヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・節約項目表示部品</t>
+    <rPh sb="1" eb="5">
+      <t>セツヤクコウモク</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>ヒョウジブヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・投資項目比較画面</t>
+    <rPh sb="1" eb="5">
+      <t>トウシコウモク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒカク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・節約項目比較画面</t>
+    <rPh sb="1" eb="9">
+      <t>セツヤクコウモクヒカクガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・当月支出遷移ボタン</t>
+    <rPh sb="1" eb="7">
+      <t>トウゲツシシュツセンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・月別支出遷移ボタン</t>
+    <rPh sb="1" eb="7">
+      <t>ツキベツシシュツセンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・年間支出遷移ボタン</t>
+    <rPh sb="1" eb="7">
+      <t>ネンカンシシュツセンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・DBからユーザーの収入を取得し表示する</t>
+    <rPh sb="10" eb="12">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・DBからユーザーの投資項目、節約項目を取得し表示する</t>
+    <rPh sb="10" eb="14">
+      <t>トウシコウモク</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>セツヤクコウモク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・収入が±指定範囲のユーザーの当月の該当項目の平均支出金額と、自身の当月の該当項目の合計を比較した画面を表示する</t>
+    <rPh sb="1" eb="3">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>シテイハンイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>トウゲツ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヘイキン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>トウゲツ</t>
+    </rPh>
+    <rPh sb="37" eb="41">
+      <t>ガイトウコウモク</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ヒカク</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・収入の設定がない場合はメッセージを表示する</t>
+    <rPh sb="1" eb="3">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・投資項目、節約項目の表示がない場合はメッセージを表示する</t>
+    <rPh sb="1" eb="5">
+      <t>トウシコウモク</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>セツヤクコウモク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・同収入帯比較画面</t>
+    <rPh sb="1" eb="5">
+      <t>ドウシュウニュウタイ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>ヒカクガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・収入が±指定範囲のユーザーの当月の支出金額の平均と、自身の当月の支出金額の合計を比較した画面を表示する</t>
+    <rPh sb="1" eb="3">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>シテイハンイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>トウゲツ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヘイキン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>トウゲツ</t>
+    </rPh>
+    <rPh sb="33" eb="37">
+      <t>シシュツキンガク</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ヒカク</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・氏名入力フォーム</t>
+    <rPh sb="1" eb="3">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・投資項目1表示部品</t>
+    <rPh sb="1" eb="5">
+      <t>トウシコウモク</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ヒョウジブヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・投資項目2表示部品</t>
+    <rPh sb="1" eb="5">
+      <t>トウシコウモク</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ヒョウジブヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・節約項目1表示部品</t>
+    <rPh sb="1" eb="5">
+      <t>セツヤクコウモク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ブヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・節約項目2表示部品</t>
+    <rPh sb="1" eb="5">
+      <t>セツヤクコウモク</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ヒョウジブヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・設定登録ボタン</t>
+    <rPh sb="1" eb="5">
+      <t>セッテイトウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日付入力フォーム</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大項目入力ドロップダウンリスト</t>
+    <rPh sb="0" eb="3">
+      <t>ダイコウモク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小項目入力ドロップダウンリスト</t>
+    <rPh sb="0" eb="3">
+      <t>ショウコウモク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金額入力フォーム</t>
+    <rPh sb="0" eb="2">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名称入力フォーム</t>
+    <rPh sb="0" eb="2">
+      <t>メイショウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支出登録ボタン</t>
+    <rPh sb="0" eb="4">
+      <t>シシュツトウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当月支出遷移ボタン</t>
+    <rPh sb="0" eb="4">
+      <t>トウゲツシシュツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>payment_data</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・DBからユーザーの氏名を取得し、氏名入力フォームに表示する</t>
+    <rPh sb="10" eb="12">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="17" eb="21">
+      <t>シメイニュウリョク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・投資項目設定ドロップダウンリスト1</t>
+    <rPh sb="1" eb="5">
+      <t>トウシコウモク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・投資項目設定ドロップダウンリスト2</t>
+    <rPh sb="1" eb="5">
+      <t>トウシコウモク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・節約項目設定ドロップダウンリスト1</t>
+    <rPh sb="1" eb="7">
+      <t>セツヤクコウモクセッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・節約項目設定ドロップダウンリスト2</t>
+    <rPh sb="1" eb="7">
+      <t>セツヤクコウモクセッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・投資、節約項目設定ドロップダウンリストを選択すると該当の項目が表示される</t>
+    <rPh sb="1" eb="3">
+      <t>トウシ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>セツヤクコウモク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・設定登録ボタンを押すと画面のフォームの情報をDBのusersに登録する</t>
+    <rPh sb="1" eb="5">
+      <t>セッテイトウロク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・登録が失敗したときはメッセージを表示し同じ画面に遷移する</t>
+    <rPh sb="1" eb="3">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・フォームの内容をもとにDBのpayment_dataにデータを登録する</t>
+    <rPh sb="6" eb="8">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・フォームの入力内容をチェックし、問題がある場合は同じ画面に遷移する</t>
+    <rPh sb="6" eb="10">
+      <t>ニュウリョクナイヨウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4456,7 +5068,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>14</v>
@@ -4494,12 +5106,102 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C6B2588-BA90-4F8D-983C-CC159D52FDE0}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:1" ht="36.6" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -4510,12 +5212,107 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8D3CDDB-8559-466E-84AE-46905D21429B}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:1" ht="36.6" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -4526,12 +5323,67 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD431F7A-5A72-48E5-8D03-640DACD1A7B8}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:1" ht="36.6" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -4726,29 +5578,29 @@
       <c r="C2" s="25"/>
       <c r="D2" s="26"/>
       <c r="O2" s="24" t="s">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="P2" s="25"/>
       <c r="Q2" s="26"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B3" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D3" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="O3" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="O3" s="21" t="s">
-        <v>67</v>
-      </c>
       <c r="P3" s="22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q3" s="23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.45">
@@ -4756,19 +5608,19 @@
         <v>44</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O4" s="13" t="s">
         <v>44</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q4" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.45">
@@ -4777,16 +5629,16 @@
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O5" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q5" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="2:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
@@ -4795,14 +5647,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O6" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P6" s="2"/>
       <c r="Q6" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
@@ -4811,19 +5663,19 @@
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I7" s="25"/>
       <c r="J7" s="26"/>
       <c r="O7" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.45">
@@ -4832,23 +5684,23 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J8" s="23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P8" s="2"/>
       <c r="Q8" s="18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.45">
@@ -4857,23 +5709,23 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.45">
@@ -4882,21 +5734,21 @@
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P10" s="2"/>
       <c r="Q10" s="18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.45">
@@ -4905,21 +5757,21 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P11" s="2"/>
       <c r="Q11" s="18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="2:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
@@ -4928,46 +5780,46 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>46</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O12" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P12" s="19"/>
       <c r="Q12" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="2:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B13" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C13" s="19"/>
       <c r="D13" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="2:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="H14" s="15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I14" s="19"/>
       <c r="J14" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -4994,32 +5846,32 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">
@@ -5029,27 +5881,27 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -5070,42 +5922,42 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.45">
@@ -5115,22 +5967,22 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -5146,57 +5998,57 @@
   <sheetData>
     <row r="1" spans="1:1" ht="36.6" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.45">
@@ -5206,22 +6058,22 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -5232,47 +6084,67 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFE29E1A-E720-45DE-8213-46E01EB83BED}">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:1" ht="36.6" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -5283,42 +6155,67 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF3CB4E6-DBF0-4C32-B8DB-B2B07996689E}">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:1" ht="36.6" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/要件定義兼設計書.xlsx
+++ b/要件定義兼設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pleiades\2026-06\workspace\springportfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145285B5-A101-409C-8804-8B865025BB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A057A8E7-6F27-4231-8F23-9D6720D3136B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="757" xr2:uid="{C9271884-C87F-40D4-9F78-D9852228CE21}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="757" activeTab="3" xr2:uid="{C9271884-C87F-40D4-9F78-D9852228CE21}"/>
   </bookViews>
   <sheets>
     <sheet name="機能要件" sheetId="1" r:id="rId1"/>
@@ -1125,16 +1125,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・当月支出データ表示リスト</t>
-    <rPh sb="1" eb="5">
-      <t>トウゲツシシュツ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・月別支出遷移ボタン</t>
     <rPh sb="1" eb="5">
       <t>ツキベツシシュツ</t>
@@ -1338,16 +1328,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・月別支出データリスト</t>
-    <rPh sb="1" eb="3">
-      <t>ツキベツ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>シシュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・当月支出遷移ボタン</t>
     <rPh sb="1" eb="5">
       <t>トウゲツシシュツ</t>
@@ -1365,13 +1345,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・年間支出データリスト</t>
-    <rPh sb="1" eb="5">
-      <t>ネンカンシシュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>支出登録</t>
     <rPh sb="0" eb="4">
       <t>シシュツトウロク</t>
@@ -1991,6 +1964,33 @@
     </rPh>
     <rPh sb="30" eb="32">
       <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・当月支出データ表示テーブル</t>
+    <rPh sb="1" eb="5">
+      <t>トウゲツシシュツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・月別支出データテーブル</t>
+    <rPh sb="1" eb="3">
+      <t>ツキベツ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・年間支出データテーブル</t>
+    <rPh sb="1" eb="5">
+      <t>ネンカンシシュツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5111,7 +5111,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="36.6" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
@@ -5121,52 +5121,52 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.45">
@@ -5176,32 +5176,32 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -5217,7 +5217,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="36.6" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
@@ -5227,7 +5227,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
@@ -5237,47 +5237,47 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.45">
@@ -5287,7 +5287,7 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.45">
@@ -5297,22 +5297,22 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -5328,7 +5328,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="36.6" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
@@ -5338,37 +5338,37 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.45">
@@ -5378,12 +5378,12 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -5578,7 +5578,7 @@
       <c r="C2" s="25"/>
       <c r="D2" s="26"/>
       <c r="O2" s="24" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="P2" s="25"/>
       <c r="Q2" s="26"/>
@@ -5967,7 +5967,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.45">
@@ -6018,32 +6018,32 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>98</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.45">
@@ -6058,22 +6058,22 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -6089,7 +6089,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="36.6" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
@@ -6099,32 +6099,32 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.45">
@@ -6134,17 +6134,17 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -6160,7 +6160,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="36.6" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
@@ -6170,32 +6170,32 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.45">
@@ -6205,17 +6205,17 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/要件定義兼設計書.xlsx
+++ b/要件定義兼設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pleiades\2026-06\workspace\springportfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A057A8E7-6F27-4231-8F23-9D6720D3136B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2675BBC7-8253-4B21-8933-CD26C39F4F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="757" activeTab="3" xr2:uid="{C9271884-C87F-40D4-9F78-D9852228CE21}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="757" xr2:uid="{C9271884-C87F-40D4-9F78-D9852228CE21}"/>
   </bookViews>
   <sheets>
     <sheet name="機能要件" sheetId="1" r:id="rId1"/>
@@ -4432,63 +4432,6 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>655320</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="3" name="コネクタ: カギ線 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{076F8EEE-2EED-28F7-4A72-731438841D26}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="7528560" y="1066800"/>
-          <a:ext cx="2659380" cy="906780"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 21920"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>129540</xdr:rowOff>
     </xdr:from>
